--- a/data/trans_bre/IP19C04-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 6,01</t>
+          <t>-7,06; 5,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 1,4</t>
+          <t>-10,6; 1,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,98</t>
+          <t>0,0; 14,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 9,79</t>
+          <t>-0,41; 9,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-54,64; —</t>
+          <t>-46,31; —</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 9,6</t>
+          <t>-8,2; 9,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,17</t>
+          <t>0,0; 10,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 3,01</t>
+          <t>-8,74; 2,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 3,08</t>
+          <t>-4,74; 3,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 431,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 9,63</t>
+          <t>-7,99; 9,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,52; -1,85</t>
+          <t>-14,76; -1,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 18,62</t>
+          <t>-1,65; 18,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 3,41</t>
+          <t>-14,42; 3,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 461,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 6,02</t>
+          <t>-5,96; 5,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 7,71</t>
+          <t>-5,02; 7,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 6,22</t>
+          <t>-2,65; 6,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 5,26</t>
+          <t>-3,43; 5,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,04; 227,39</t>
+          <t>-66,89; 177,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,28; 192,65</t>
+          <t>-54,46; 189,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,54; 327,59</t>
+          <t>-49,01; 428,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,41; 261,74</t>
+          <t>-63,47; 291,23</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 0,72</t>
+          <t>-12,46; 0,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 12,38</t>
+          <t>-2,66; 14,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 11,48</t>
+          <t>-1,06; 10,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 11,45</t>
+          <t>0,45; 11,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 71,06</t>
+          <t>-100,0; 80,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,48; 341,36</t>
+          <t>-32,36; 404,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-55,95; —</t>
+          <t>-51,57; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 6,5</t>
+          <t>-12,26; 6,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 8,57</t>
+          <t>-8,46; 9,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,97; -1,88</t>
+          <t>-25,24; -2,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 15,61</t>
+          <t>-5,83; 16,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 464,0</t>
+          <t>-100,0; 375,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 68,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 1,22</t>
+          <t>-4,25; 1,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 4,17</t>
+          <t>-2,34; 3,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,96</t>
+          <t>-1,36; 3,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,19</t>
+          <t>-0,48; 4,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-53,6; 31,61</t>
+          <t>-52,75; 31,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 105,17</t>
+          <t>-31,41; 92,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 156,53</t>
+          <t>-27,46; 143,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 221,51</t>
+          <t>-14,26; 242,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 5,27</t>
+          <t>-7,1; 5,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 1,32</t>
+          <t>-9,93; 1,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,04</t>
+          <t>0,0; 13,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 9,93</t>
+          <t>-0,34; 9,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-46,31; —</t>
+          <t>-57,27; —</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 9,1</t>
+          <t>-8,17; 10,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,59</t>
+          <t>0,0; 11,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 2,6</t>
+          <t>-8,29; 3,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 3,21</t>
+          <t>-5,1; 2,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 431,5</t>
+          <t>-85,6; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 9,88</t>
+          <t>-8,18; 9,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,76; -1,57</t>
+          <t>-14,43; -1,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 18,41</t>
+          <t>-1,81; 19,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 3,77</t>
+          <t>-14,92; 4,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 5,6</t>
+          <t>-5,53; 5,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 7,85</t>
+          <t>-5,2; 8,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 6,75</t>
+          <t>-3,26; 6,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 5,77</t>
+          <t>-3,97; 5,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,89; 177,19</t>
+          <t>-65,18; 189,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,46; 189,15</t>
+          <t>-53,7; 218,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,01; 428,09</t>
+          <t>-54,77; 330,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,47; 291,23</t>
+          <t>-65,03; 322,52</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 0,5</t>
+          <t>-11,86; 1,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 14,56</t>
+          <t>-2,87; 12,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 10,93</t>
+          <t>-0,64; 10,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 11,25</t>
+          <t>0,84; 11,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 80,65</t>
+          <t>-100,0; 84,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 404,28</t>
+          <t>-32,24; 358,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-51,57; —</t>
+          <t>-45,13; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 6,06</t>
+          <t>-12,36; 4,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 9,75</t>
+          <t>-8,75; 10,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,24; -2,61</t>
+          <t>-24,89; -1,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 16,11</t>
+          <t>-5,0; 15,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 375,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,01</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 1,57</t>
+          <t>-4,3; 1,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,7</t>
+          <t>-2,23; 3,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,93</t>
+          <t>-1,29; 3,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,41</t>
+          <t>-0,27; 4,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-52,75; 31,36</t>
+          <t>-53,49; 34,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 92,52</t>
+          <t>-32,36; 87,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 143,35</t>
+          <t>-28,63; 132,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 242,61</t>
+          <t>-9,22; 217,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>235,68%</t>
+          <t>187,57%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 5,65</t>
+          <t>-7,15; 6,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 1,37</t>
+          <t>-10,78; 1,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,85</t>
+          <t>0,0; 12,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 9,87</t>
+          <t>-0,97; 9,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-57,27; —</t>
+          <t>-60,68; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-18,28%</t>
+          <t>-3,28%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 10,23</t>
+          <t>-9,3; 9,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,09</t>
+          <t>0,0; 10,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 3,13</t>
+          <t>-8,45; 3,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 2,68</t>
+          <t>-3,75; 3,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,6; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,31</t>
+          <t>-3,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-62,68%</t>
+          <t>-60,18%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 9,47</t>
+          <t>-8,36; 9,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,43; -1,6</t>
+          <t>-14,52; -1,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 19,08</t>
+          <t>-1,65; 18,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 4,56</t>
+          <t>-13,78; 4,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 461,51</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 5,78</t>
+          <t>-5,16; 6,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 8,38</t>
+          <t>-5,31; 7,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 6,16</t>
+          <t>-2,99; 6,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 5,69</t>
+          <t>-3,33; 6,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,18; 189,2</t>
+          <t>-62,04; 227,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,7; 218,44</t>
+          <t>-54,28; 192,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,77; 330,5</t>
+          <t>-55,54; 327,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 322,52</t>
+          <t>-61,57; 328,78</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,7</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>395,89%</t>
+          <t>405,46%</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 1,77</t>
+          <t>-12,68; 0,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 12,97</t>
+          <t>-3,82; 12,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 10,65</t>
+          <t>-0,64; 11,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 11,58</t>
+          <t>0,49; 12,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 84,42</t>
+          <t>-100,0; 71,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,24; 358,76</t>
+          <t>-38,48; 341,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-45,13; —</t>
+          <t>-55,95; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>-37,82%</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 4,56</t>
+          <t>-12,53; 6,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 10,04</t>
+          <t>-8,9; 8,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,89; -1,88</t>
+          <t>-24,97; -1,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 15,5</t>
+          <t>-10,46; 3,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 464,0</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>52,75%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,58</t>
+          <t>-4,42; 1,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,62</t>
+          <t>-1,89; 4,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,85</t>
+          <t>-1,27; 3,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,31</t>
+          <t>-0,64; 3,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-53,49; 34,04</t>
+          <t>-53,6; 31,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 87,02</t>
+          <t>-29,91; 105,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-28,63; 132,05</t>
+          <t>-25,9; 156,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 217,2</t>
+          <t>-20,31; 194,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,173 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-3,15</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,86</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,73</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-9,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-69,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>187,57%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.4033212024699327</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-3.151895651087151</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.86377649477073</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.727683103998178</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.09537571524159355</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.692436767931233</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.875699808893919</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,15; 6,01</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-10,78; 1,4</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,98</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-0,97; 9,02</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-60,68; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.148462637298931</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-10.77572837623674</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-0.973478434454858</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-0.6067771198488187</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.005395896436239</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.404182312826357</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12.97841122383543</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9.020913553338586</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,26</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,85</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,26%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-44,37%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-3,28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-9,3; 9,6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,17</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-8,45; 3,01</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,75; 3,45</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.0728270883851</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.259330562817781</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.854980396546293</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.05875292146382931</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1825582259730214</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.4436781508757393</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.03279992484543331</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-6,4</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,93</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,91</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,96%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>187,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-60,18%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-9.304103012939127</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-8.445069469598174</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.747847710865769</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-8,36; 9,63</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-14,52; -1,85</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,65; 18,62</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-13,78; 4,08</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 461,51</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.604059274395313</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10.16643437984817</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.011638038765773</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.446150463964336</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +793,189 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>33,08%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.4619519982911241</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-6.404939597715356</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6.926528467982973</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.912580871819173</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.0695519573894785</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1.877819402396421</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.6018372939781196</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,16; 6,02</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,31; 7,71</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,99; 6,22</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,33; 6,21</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-62,04; 227,39</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-54,28; 192,65</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-55,54; 327,59</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-61,57; 328,78</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8.364681640281104</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-14.51730424749312</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.647483032396114</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-13.78330179923547</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.627910518364796</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-1.848032413752782</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>18.62134636881081</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.083280916871574</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>4.615066133901817</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-5,65</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,99</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-66,49%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>69,44%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>204,81%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>405,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-12,68; 0,72</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,82; 12,38</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,64; 11,48</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,49; 12,35</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 71,06</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-38,48; 341,36</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-55,95; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.0248345419482994</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.518764777454904</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.680874141413007</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.30300351634127</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.003961215253579654</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.211902289673962</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.4354478676387938</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.3308429385298739</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-2,42</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-11,9</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-33,51%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-5,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-84,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-37,82%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.155527106946531</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.31249483416541</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.98647958023596</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.328662560128165</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6204233788996377</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5427573833825128</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5553767909940864</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6156515348272761</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-12,53; 6,5</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-8,9; 8,57</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-24,97; -1,88</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-10,46; 3,64</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 464,0</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.023447084907932</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.714287469435649</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.221474439767846</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.214822087053086</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.273853802425038</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.92651587616975</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>3.275927483589795</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>3.28781145938905</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +983,283 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-1,38</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-21,14%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>52,75%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-5.646666674963749</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>5.068751271064601</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>4.60470049941286</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>4.987615532379801</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.6648988538217806</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.6943613735832208</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>2.048096216746202</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>4.054570882897815</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-4,42; 1,22</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-1,89; 4,17</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,27; 3,96</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,64; 3,78</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-53,6; 31,61</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-29,91; 105,17</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-25,9; 156,53</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-20,31; 194,96</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-12.6753262331398</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.824907755742041</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.6430725072837157</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.4902997388595909</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3848421621742867</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.5594861382321832</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.7181373810768223</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>12.38125174190384</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>11.47511755043773</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>12.34565797092548</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.7106010103371045</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>3.413577479769653</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-2.419244865892583</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-0.2805159331385788</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-11.89540565569638</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.602250387630242</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3351022229555493</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.05277613307180112</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.849522798902836</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.3781616237631064</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-12.53444736814914</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-8.901366185369998</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-24.96943463301907</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-10.46454263727005</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>6.503012379204804</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>8.566257694760752</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-1.876052904155342</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>3.643242571395323</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>4.640039303957441</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-1.383337933139115</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.9369157519978701</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.279889580212112</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.520621282529025</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.2113509903971081</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.1708615670376631</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.3257152597769625</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.5275383617664849</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-4.423407150987582</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.89453238362053</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.269356030895269</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.6425943412588666</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.536043357527366</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.2991398488036579</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.2590225910976155</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.2031416166735816</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.222245144184295</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4.170084597311993</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.961322980691624</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.779768832699958</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.3161307209925281</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1.051670374577716</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1.56527429451803</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>1.949595424568873</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1267,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
